--- a/Day-9(9-03)/apiTestCases.xlsx
+++ b/Day-9(9-03)/apiTestCases.xlsx
@@ -4,7 +4,6 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Sheet2" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="51">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -277,135 +276,6 @@
 2. The successfull deletion message is returned as a JSON.
 3. The response time is within 200ms.</t>
   </si>
-  <si>
-    <t>Pass/Fail</t>
-  </si>
-  <si>
-    <t>Validate successful PUT request to completely update an existing object.</t>
-  </si>
-  <si>
-    <t>URL: &lt;https://api.restful.dev/objects/7&gt; BODY: { "name": "New Name 2026", "year": 2026, "price": 1000 }</t>
-  </si>
-  <si>
-    <t>1. User selects the PUT method. 2. User enters the URL with a valid existing object ID. 3. User enters a valid JSON body with all required updated data. 4. User sends the request.</t>
-  </si>
-  <si>
-    <t>1. Status code must be "200 OK". 2. The returned object must contain the updated data and replace all previous fields. 3. Response time within 200ms.</t>
-  </si>
-  <si>
-    <t>Base URL</t>
-  </si>
-  <si>
-    <t>Validate PUT request with missing required field (Negative).</t>
-  </si>
-  <si>
-    <t>URL: &lt;https://api.restful.dev/objects/7&gt; BODY: { "name": "New Name", "price": 1000 }</t>
-  </si>
-  <si>
-    <t>1. User selects the PUT method. 2. User enters the URL with a valid object ID. 3. User enters a JSON body missing a required field (e.g., "year"). 4. User sends the request.</t>
-  </si>
-  <si>
-    <t>1. Status code must be "400 Bad Request" or "422 Unprocessable Entity". 2. Error message explaining the required field is missing.</t>
-  </si>
-  <si>
-    <t>Validate successful PATCH request to update a single field of an existing object.</t>
-  </si>
-  <si>
-    <t>URL: &lt;https://api.restful.dev/objects/7&gt; BODY: { "studio": "New Studio Productions" }</t>
-  </si>
-  <si>
-    <t>1. User selects the PATCH method. 2. User enters the URL with a valid existing object ID. 3. User enters a valid JSON body with only the partial data to update. 4. User sends the request.</t>
-  </si>
-  <si>
-    <t>1. Status code must be "200 OK". 2. The returned object must show the updated field while retaining all other non-updated fields. 3. Response time within 200ms.</t>
-  </si>
-  <si>
-    <t>Validate PATCH request with malformed JSON structure (Negative).</t>
-  </si>
-  <si>
-    <t>URL: &lt;https://api.restful.dev/objects/7&gt; BODY: { "studio": "New Studio" } // Missing closing bracket</t>
-  </si>
-  <si>
-    <t>1. User selects the PATCH method. 2. User enters the URL with a valid object ID. 3. User enters a malformed JSON body (e.g., syntax error). 4. User sends the request.</t>
-  </si>
-  <si>
-    <t>1. Status code must be "400 Bad Request". 2. Error message indicating invalid input format or JSON syntax error.</t>
-  </si>
-  <si>
-    <t>TC_07</t>
-  </si>
-  <si>
-    <t>URL: &lt;https://api.restful.dev/objects/7&gt;</t>
-  </si>
-  <si>
-    <t>1. User selects the DELETE method. 2. User enters the URL with a valid existing object ID. 3. User sends the request. 4. User performs a subsequent GET request on the same ID.</t>
-  </si>
-  <si>
-    <t>1. Status code must be "200 OK" or "204 No Content" for the DELETE. 2. Subsequent GET request must return "404 Not Found", confirming deletion. 3. Response time within 200ms.</t>
-  </si>
-  <si>
-    <t>TC_08</t>
-  </si>
-  <si>
-    <t>Validate DELETE request on an object ID with improper access rights (Negative).</t>
-  </si>
-  <si>
-    <t>URL: &lt;https://api.restful.dev/objects/5&gt; (Requires Admin Token)</t>
-  </si>
-  <si>
-    <t>1. User selects the DELETE method. 2. User enters the URL with an object ID they do not have permission to delete. 3. User sends the request without the required authentication or with a wrong token.</t>
-  </si>
-  <si>
-    <t>1. Status code must be "401 Unauthorized" or "403 Forbidden". 2. Error message explaining the user lacks necessary permissions.</t>
-  </si>
-  <si>
-    <t>TC_09</t>
-  </si>
-  <si>
-    <t>Validate DELETE request on a non-existent object ID (Negative).</t>
-  </si>
-  <si>
-    <t>URL: &lt;https://api.restful.dev/objects/9999&gt;</t>
-  </si>
-  <si>
-    <t>1. User selects the DELETE method. 2. User enters the URL with a non-existent object ID. 3. User sends the request.</t>
-  </si>
-  <si>
-    <t>1. Status code must be "404 Not Found" or appropriate error code. 2. Error message explaining the resource is not found.</t>
-  </si>
-  <si>
-    <t>TC_10</t>
-  </si>
-  <si>
-    <t>Validate PUT request to a non-existent object ID (Attempted Creation - Negative/Dependent).</t>
-  </si>
-  <si>
-    <t>URL: &lt;https://api.restful.dev/objects/9999&gt; BODY: { "name": "New Item", "year": 2026, "price": 500 }</t>
-  </si>
-  <si>
-    <t>1. User selects the PUT method. 2. User enters the URL with a non-existent object ID. 3. User enters a complete valid JSON body. 4. User sends the request.</t>
-  </si>
-  <si>
-    <t>1. Status code must be "404 Not Found" (if PUT is strictly update) or "201 Created" (if PUT allows creation). Assuming strictly update, "404 Not Found".</t>
-  </si>
-  <si>
-    <t>TC_11</t>
-  </si>
-  <si>
-    <t>Base URL, Existing Object ID, Read-Only Field</t>
-  </si>
-  <si>
-    <t>Validate PATCH request attempting to update a read-only field (Negative).</t>
-  </si>
-  <si>
-    <t>URL: &lt;https://api.restful.dev/objects/7&gt; BODY: { "createdAt": "2024-01-01T00:00:00Z" }</t>
-  </si>
-  <si>
-    <t>1. User selects the PATCH method. 2. User enters the URL with a valid object ID. 3. User attempts to modify a server-generated/read-only field. 4. User sends the request.</t>
-  </si>
-  <si>
-    <t>1. Status code must be "400 Bad Request" or "403 Forbidden". 2. Error message indicating that the field is read-only or immutable.</t>
-  </si>
 </sst>
 </file>
 
@@ -454,7 +324,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="13">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -494,27 +364,11 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="3">
     <dxf>
       <font/>
       <fill>
@@ -542,53 +396,17 @@
       </fill>
       <border/>
     </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF535FC1"/>
-          <bgColor rgb="FF535FC1"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF535FC1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF535FC1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF535FC1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF535FC1"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
-  <tableStyles count="2">
+  <tableStyles count="1">
     <tableStyle count="2" pivot="0" name="Sheet1-style">
       <tableStyleElement dxfId="1" type="firstRowStripe"/>
       <tableStyleElement dxfId="2" type="secondRowStripe"/>
-    </tableStyle>
-    <tableStyle count="4" pivot="0" name="Sheet2-style">
-      <tableStyleElement dxfId="3" type="headerRow"/>
-      <tableStyleElement dxfId="1" type="firstRowStripe"/>
-      <tableStyleElement dxfId="2" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -608,22 +426,6 @@
     <tableColumn name="Column7" id="7"/>
   </tableColumns>
   <tableStyleInfo name="Sheet1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="B3:I12" displayName="Table1" name="Table1" id="2">
-  <tableColumns count="8">
-    <tableColumn name="Test Case ID" id="1"/>
-    <tableColumn name="Module Name" id="2"/>
-    <tableColumn name="Pre-Requisite" id="3"/>
-    <tableColumn name="Test Case Name" id="4"/>
-    <tableColumn name="Test Data" id="5"/>
-    <tableColumn name="Test Steps" id="6"/>
-    <tableColumn name="Expected Result" id="7"/>
-    <tableColumn name="Pass/Fail" id="8"/>
-  </tableColumns>
-  <tableStyleInfo name="Sheet2-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -10962,311 +10764,4 @@
     <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="1" max="2" width="18.63"/>
-    <col customWidth="1" min="3" max="3" width="18.5"/>
-    <col customWidth="1" min="4" max="8" width="18.63"/>
-    <col customWidth="1" min="9" max="9" width="16.5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="13"/>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-    </row>
-    <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="13"/>
-      <c r="B3" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="13"/>
-      <c r="B4" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="I4" s="18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="13"/>
-      <c r="B5" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="I5" s="18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="13"/>
-      <c r="B6" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="I6" s="18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="13"/>
-      <c r="B7" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="I7" s="18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="13"/>
-      <c r="B8" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="I8" s="18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="22.5" customHeight="1">
-      <c r="B9" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="I9" s="18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="22.5" customHeight="1">
-      <c r="B10" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="I10" s="18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="B11" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="G11" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="I11" s="18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="22.5" customHeight="1">
-      <c r="B12" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="I12" s="18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <drawing r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId3"/>
-  </tableParts>
-</worksheet>
 </file>